--- a/data/trans_orig/P23_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>128941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168493</t>
+          <t>167484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71130</t>
+          <t>71863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101440</t>
+          <t>103330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209428</t>
+          <t>207538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261006</t>
+          <t>259078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305283</t>
+          <t>306292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347171</t>
+          <t>344835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205240</t>
+          <t>203350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235550</t>
+          <t>234817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519451</t>
+          <t>521379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>571029</t>
+          <t>572919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109474</t>
+          <t>109542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>146398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112954</t>
+          <t>112695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149078</t>
+          <t>150854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>230792</t>
+          <t>229341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285059</t>
+          <t>282664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220761</t>
+          <t>220536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257460</t>
+          <t>257392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>221011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258911</t>
+          <t>259170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>453740</t>
+          <t>456135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>508007</t>
+          <t>509458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221166</t>
+          <t>222737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270042</t>
+          <t>268219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56071</t>
+          <t>55986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263376</t>
+          <t>263930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>317229</t>
+          <t>315102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272347</t>
+          <t>274170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321223</t>
+          <t>319652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111711</t>
+          <t>111796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134160</t>
+          <t>134115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>392942</t>
+          <t>395069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>446795</t>
+          <t>446241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>493663</t>
+          <t>498361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>562018</t>
+          <t>567586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204601</t>
+          <t>201342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252465</t>
+          <t>251249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>714301</t>
+          <t>713033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>798786</t>
+          <t>799986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676316</t>
+          <t>670748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>744671</t>
+          <t>739973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461820</t>
+          <t>463036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>509684</t>
+          <t>512943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1153834</t>
+          <t>1152634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238319</t>
+          <t>1239587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151302</t>
+          <t>150811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189517</t>
+          <t>188724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153240</t>
+          <t>152923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198689</t>
+          <t>197827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>313331</t>
+          <t>311770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375197</t>
+          <t>376679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161038</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199253</t>
+          <t>199744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370063</t>
+          <t>370925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415512</t>
+          <t>415829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>544110</t>
+          <t>542628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605976</t>
+          <t>607537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66912</t>
+          <t>66680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97393</t>
+          <t>96921</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>142270</t>
+          <t>144606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>189561</t>
+          <t>192534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>220598</t>
+          <t>220818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>276535</t>
+          <t>277433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>200237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230246</t>
+          <t>230478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1059199</t>
+          <t>1056226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1106490</t>
+          <t>1104154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1269383</t>
+          <t>1268485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1325320</t>
+          <t>1325100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1244566</t>
+          <t>1245912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1360393</t>
+          <t>1359202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>782346</t>
+          <t>774418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>884239</t>
+          <t>874238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2054883</t>
+          <t>2055773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2210608</t>
+          <t>2211750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1908755</t>
+          <t>1909946</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2024582</t>
+          <t>2023236</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2493885</t>
+          <t>2503886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2595778</t>
+          <t>2603706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4436664</t>
+          <t>4435522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4592389</t>
+          <t>4591499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120496</t>
+          <t>121463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163545</t>
+          <t>165337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79537</t>
+          <t>78880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111950</t>
+          <t>112950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211129</t>
+          <t>208841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266176</t>
+          <t>262372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273666</t>
+          <t>271874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>316715</t>
+          <t>315748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>201504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234917</t>
+          <t>235574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485489</t>
+          <t>489293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540536</t>
+          <t>542824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125138</t>
+          <t>125408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166946</t>
+          <t>164670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106917</t>
+          <t>105792</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143499</t>
+          <t>143297</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240123</t>
+          <t>242700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>298886</t>
+          <t>298289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>251851</t>
+          <t>254127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>293659</t>
+          <t>293389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194512</t>
+          <t>194714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231094</t>
+          <t>232219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457922</t>
+          <t>458519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>516685</t>
+          <t>514108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>226758</t>
+          <t>227801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>277876</t>
+          <t>279092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>68413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99431</t>
+          <t>99124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304710</t>
+          <t>303821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366015</t>
+          <t>366364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>351539</t>
+          <t>350323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>402657</t>
+          <t>401614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160698</t>
+          <t>161005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191787</t>
+          <t>191716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>523529</t>
+          <t>523180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584834</t>
+          <t>585723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>434646</t>
+          <t>430030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>502378</t>
+          <t>498395</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254175</t>
+          <t>253722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>310129</t>
+          <t>309694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>702947</t>
+          <t>704464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>793352</t>
+          <t>794417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>655602</t>
+          <t>659585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>723334</t>
+          <t>727950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455532</t>
+          <t>455967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511486</t>
+          <t>511939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1130289</t>
+          <t>1129224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220694</t>
+          <t>1219177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179826</t>
+          <t>181082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227089</t>
+          <t>226362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188698</t>
+          <t>191284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240533</t>
+          <t>242376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380933</t>
+          <t>384276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>449384</t>
+          <t>454562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>283507</t>
+          <t>284234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330770</t>
+          <t>329514</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520003</t>
+          <t>518160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>571838</t>
+          <t>569252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>821748</t>
+          <t>816570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890199</t>
+          <t>886856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41203</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66998</t>
+          <t>66750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136930</t>
+          <t>136311</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182863</t>
+          <t>183319</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186291</t>
+          <t>184592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236532</t>
+          <t>236247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199884</t>
+          <t>200132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225679</t>
+          <t>226588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>926488</t>
+          <t>926032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>972421</t>
+          <t>973040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1139701</t>
+          <t>1139986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1189942</t>
+          <t>1191641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1201337</t>
+          <t>1204633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1322118</t>
+          <t>1322620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>902534</t>
+          <t>900642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1017702</t>
+          <t>1014551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2136229</t>
+          <t>2145018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2299280</t>
+          <t>2309708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2098762</t>
+          <t>2098260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2219543</t>
+          <t>2216247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2530441</t>
+          <t>2533592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2645609</t>
+          <t>2647501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4669744</t>
+          <t>4659316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4832795</t>
+          <t>4824006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88873</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125404</t>
+          <t>127090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>53839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82960</t>
+          <t>82368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151802</t>
+          <t>150389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200841</t>
+          <t>197527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303688</t>
+          <t>302002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340219</t>
+          <t>340000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264095</t>
+          <t>264687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294574</t>
+          <t>293216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575306</t>
+          <t>578620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624345</t>
+          <t>625758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89197</t>
+          <t>88888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123656</t>
+          <t>123920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83402</t>
+          <t>82401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119324</t>
+          <t>118369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180516</t>
+          <t>180979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231657</t>
+          <t>230292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>252499</t>
+          <t>252235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>286958</t>
+          <t>287267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251922</t>
+          <t>252877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287844</t>
+          <t>288845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>515744</t>
+          <t>517109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>566885</t>
+          <t>566422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193497</t>
+          <t>194585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241300</t>
+          <t>240601</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>66328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243660</t>
+          <t>243796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294742</t>
+          <t>297949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280614</t>
+          <t>281313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328417</t>
+          <t>327329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100854</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124716</t>
+          <t>125578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>393294</t>
+          <t>390087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444376</t>
+          <t>444240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>396635</t>
+          <t>395236</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>461436</t>
+          <t>464370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288381</t>
+          <t>288694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>343131</t>
+          <t>344372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>703424</t>
+          <t>703002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>788286</t>
+          <t>789920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>687338</t>
+          <t>684404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>752139</t>
+          <t>753538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>480576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>536567</t>
+          <t>536254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1185436</t>
+          <t>1183802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1270298</t>
+          <t>1270720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217673</t>
+          <t>217059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265690</t>
+          <t>267129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192356</t>
+          <t>191632</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242214</t>
+          <t>241617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>423574</t>
+          <t>423617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>495037</t>
+          <t>491331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>355016</t>
+          <t>353577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403033</t>
+          <t>403647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>494941</t>
+          <t>495538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544799</t>
+          <t>545523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>862824</t>
+          <t>866530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>934287</t>
+          <t>934244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>57717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89135</t>
+          <t>87936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150392</t>
+          <t>146775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198583</t>
+          <t>200319</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>216633</t>
+          <t>215497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>273373</t>
+          <t>274893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198010</t>
+          <t>199209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228868</t>
+          <t>229428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>881047</t>
+          <t>879311</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>929238</t>
+          <t>932855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1093402</t>
+          <t>1091882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1150142</t>
+          <t>1151278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1119772</t>
+          <t>1114959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1230762</t>
+          <t>1232237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>873807</t>
+          <t>863563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>982243</t>
+          <t>972091</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2008379</t>
+          <t>2016271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2173519</t>
+          <t>2170113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2153023</t>
+          <t>2151548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2264013</t>
+          <t>2268826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2543914</t>
+          <t>2554066</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2652350</t>
+          <t>2662594</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4736424</t>
+          <t>4739830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4901564</t>
+          <t>4893672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103291</t>
+          <t>104086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57389</t>
+          <t>57619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133268</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177924</t>
+          <t>180077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401921</t>
+          <t>401126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435782</t>
+          <t>437242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>364165</t>
+          <t>364625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>390078</t>
+          <t>389848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774755</t>
+          <t>772602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>819411</t>
+          <t>817461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75813</t>
+          <t>76825</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111866</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100615</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153353</t>
+          <t>152685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199748</t>
+          <t>198784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340347</t>
+          <t>337314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376400</t>
+          <t>375388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281965</t>
+          <t>283603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311282</t>
+          <t>312479</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>635045</t>
+          <t>636009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681440</t>
+          <t>682108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>50170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199836</t>
+          <t>203009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61589</t>
+          <t>76096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212240</t>
+          <t>214137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468428</t>
+          <t>465255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622983</t>
+          <t>618094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132625</t>
+          <t>133380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147705</t>
+          <t>148184</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622935</t>
+          <t>621038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>773586</t>
+          <t>759079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>301914</t>
+          <t>302702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>372254</t>
+          <t>374876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120307</t>
+          <t>106548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279731</t>
+          <t>278875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371811</t>
+          <t>348963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>630452</t>
+          <t>630951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>662565</t>
+          <t>659943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>732905</t>
+          <t>732117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697700</t>
+          <t>698556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>857124</t>
+          <t>870883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1381798</t>
+          <t>1381299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1640439</t>
+          <t>1663287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137937</t>
+          <t>137367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182763</t>
+          <t>181140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119686</t>
+          <t>120705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186185</t>
+          <t>187122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259615</t>
+          <t>263009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>355536</t>
+          <t>357680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291253</t>
+          <t>292876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336079</t>
+          <t>336649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654469</t>
+          <t>653532</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720968</t>
+          <t>719949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>959134</t>
+          <t>956990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1055055</t>
+          <t>1051661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69307</t>
+          <t>70758</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105038</t>
+          <t>106932</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92772</t>
+          <t>92873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>142299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188211</t>
+          <t>190644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222705</t>
+          <t>225652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>656333</t>
+          <t>654439</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>692064</t>
+          <t>690613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>858193</t>
+          <t>858576</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>908103</t>
+          <t>908002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>638398</t>
+          <t>592456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>915271</t>
+          <t>910701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>516389</t>
+          <t>526310</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>697232</t>
+          <t>698694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1234298</t>
+          <t>1253799</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1577745</t>
+          <t>1576625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2458757</t>
+          <t>2463327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2735630</t>
+          <t>2781572</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2879182</t>
+          <t>2877720</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3060025</t>
+          <t>3050104</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5372696</t>
+          <t>5373816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5716143</t>
+          <t>5696642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128941</t>
+          <t>129442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167484</t>
+          <t>170095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>71494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103330</t>
+          <t>103475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207538</t>
+          <t>208657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259078</t>
+          <t>260391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306292</t>
+          <t>303681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344835</t>
+          <t>344334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203350</t>
+          <t>203205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234817</t>
+          <t>235186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521379</t>
+          <t>520066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572919</t>
+          <t>571800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109542</t>
+          <t>108284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146398</t>
+          <t>145173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112695</t>
+          <t>111817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150854</t>
+          <t>148972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229341</t>
+          <t>231989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>282664</t>
+          <t>284717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>220536</t>
+          <t>221761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257392</t>
+          <t>258650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221011</t>
+          <t>222893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259170</t>
+          <t>260048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>456135</t>
+          <t>454082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509458</t>
+          <t>506810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>222737</t>
+          <t>222015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268219</t>
+          <t>269167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55986</t>
+          <t>55868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263930</t>
+          <t>264471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315102</t>
+          <t>318289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274170</t>
+          <t>273222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319652</t>
+          <t>320374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111796</t>
+          <t>111914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134115</t>
+          <t>134305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>395069</t>
+          <t>391882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>446241</t>
+          <t>445700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>498361</t>
+          <t>495158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>567586</t>
+          <t>565750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201342</t>
+          <t>206312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251249</t>
+          <t>254544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>713033</t>
+          <t>714322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>799986</t>
+          <t>802105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>670748</t>
+          <t>672584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>739973</t>
+          <t>743176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463036</t>
+          <t>459741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512943</t>
+          <t>507973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152634</t>
+          <t>1150515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1239587</t>
+          <t>1238298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150811</t>
+          <t>151849</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188724</t>
+          <t>188891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152923</t>
+          <t>151409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197827</t>
+          <t>196765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>311770</t>
+          <t>315130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376679</t>
+          <t>372791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161831</t>
+          <t>161664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199744</t>
+          <t>198706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370925</t>
+          <t>371987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415829</t>
+          <t>417343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>542628</t>
+          <t>546516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>607537</t>
+          <t>604177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>66348</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96921</t>
+          <t>96007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>144606</t>
+          <t>145318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>192534</t>
+          <t>190442</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>220818</t>
+          <t>219723</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>277433</t>
+          <t>281152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200237</t>
+          <t>201151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230478</t>
+          <t>230810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1056226</t>
+          <t>1058318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1104154</t>
+          <t>1103442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1268485</t>
+          <t>1264766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1325100</t>
+          <t>1326195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1245912</t>
+          <t>1249875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1359202</t>
+          <t>1357754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>774418</t>
+          <t>777890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>874238</t>
+          <t>875875</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2055773</t>
+          <t>2054238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2211750</t>
+          <t>2205661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1909946</t>
+          <t>1911394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2023236</t>
+          <t>2019273</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2503886</t>
+          <t>2502249</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2603706</t>
+          <t>2600234</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4435522</t>
+          <t>4441611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4591499</t>
+          <t>4593034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121463</t>
+          <t>121631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165337</t>
+          <t>163116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78880</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112950</t>
+          <t>113324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208841</t>
+          <t>209499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262372</t>
+          <t>264352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271874</t>
+          <t>274095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315748</t>
+          <t>315580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201504</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235574</t>
+          <t>235895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>489293</t>
+          <t>487313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>542824</t>
+          <t>542166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125408</t>
+          <t>122941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164670</t>
+          <t>166327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105792</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143297</t>
+          <t>142378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242700</t>
+          <t>240310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>298289</t>
+          <t>294662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254127</t>
+          <t>252470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>293389</t>
+          <t>295856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194714</t>
+          <t>195633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232219</t>
+          <t>233029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>458519</t>
+          <t>462146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>514108</t>
+          <t>516498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>227801</t>
+          <t>229349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>279092</t>
+          <t>280140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68413</t>
+          <t>68535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99124</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303821</t>
+          <t>306699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366364</t>
+          <t>363676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350323</t>
+          <t>349275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>401614</t>
+          <t>400066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161005</t>
+          <t>162326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>191716</t>
+          <t>191594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>523180</t>
+          <t>525868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>585723</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>430030</t>
+          <t>434296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>498395</t>
+          <t>501064</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253722</t>
+          <t>254476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>309694</t>
+          <t>311048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>704464</t>
+          <t>700549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>794417</t>
+          <t>790289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>659585</t>
+          <t>656916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>727950</t>
+          <t>723684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455967</t>
+          <t>454613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511939</t>
+          <t>511185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1129224</t>
+          <t>1133352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1219177</t>
+          <t>1223092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181082</t>
+          <t>180506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226362</t>
+          <t>225208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,82 +4755,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>35,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>214412</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>187401</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>242690</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>24,64%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>31,91%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>416280</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>382966</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>450685</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>32,75%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>35,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>214412</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>191284</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>242376</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>416280</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>384276</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>454562</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>30,23%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284234</t>
+          <t>285388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>329514</t>
+          <t>330090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,82 +4868,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>64,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>546124</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>517846</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>573135</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>68,09%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>75,36%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>854852</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>820447</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>888166</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>67,25%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>64,54%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>546124</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>518160</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>569252</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>74,85%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>854852</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>816570</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>886856</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>64,24%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>39190</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66750</t>
+          <t>65942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183319</t>
+          <t>182589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184592</t>
+          <t>184812</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236247</t>
+          <t>238402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200132</t>
+          <t>200940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226588</t>
+          <t>227692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>926032</t>
+          <t>926762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>973040</t>
+          <t>974092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1139986</t>
+          <t>1137831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1191641</t>
+          <t>1191421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1204633</t>
+          <t>1205138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1322620</t>
+          <t>1319841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>900642</t>
+          <t>903959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1014551</t>
+          <t>1015863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2145018</t>
+          <t>2139883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2309708</t>
+          <t>2305412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2098260</t>
+          <t>2101039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2216247</t>
+          <t>2215742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2533592</t>
+          <t>2532280</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2647501</t>
+          <t>2644184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4659316</t>
+          <t>4663612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4824006</t>
+          <t>4829141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89092</t>
+          <t>89073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127090</t>
+          <t>126450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82368</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150389</t>
+          <t>150202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197527</t>
+          <t>199719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302002</t>
+          <t>302642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340000</t>
+          <t>340019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264687</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293216</t>
+          <t>293509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>578620</t>
+          <t>576428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>625758</t>
+          <t>625945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88888</t>
+          <t>87291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123920</t>
+          <t>125692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82401</t>
+          <t>85114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>118682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180979</t>
+          <t>182302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>230292</t>
+          <t>232708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>252235</t>
+          <t>250463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287267</t>
+          <t>288864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252877</t>
+          <t>252564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288845</t>
+          <t>286132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>517109</t>
+          <t>514693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>566422</t>
+          <t>565099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194585</t>
+          <t>195167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240601</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>65103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243796</t>
+          <t>242817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297949</t>
+          <t>295807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281313</t>
+          <t>280931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327329</t>
+          <t>326747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99795</t>
+          <t>101020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125578</t>
+          <t>124944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390087</t>
+          <t>392229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444240</t>
+          <t>445219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>395236</t>
+          <t>398423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>464370</t>
+          <t>464749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288694</t>
+          <t>289140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344372</t>
+          <t>343617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>703002</t>
+          <t>705088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>789920</t>
+          <t>788656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>684404</t>
+          <t>684025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>753538</t>
+          <t>750351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>480576</t>
+          <t>481331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>536254</t>
+          <t>535808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183802</t>
+          <t>1185066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1270720</t>
+          <t>1268634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,28%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>217059</t>
+          <t>218970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267129</t>
+          <t>265608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191632</t>
+          <t>193473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241617</t>
+          <t>243265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>423617</t>
+          <t>421991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>491331</t>
+          <t>491431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>353577</t>
+          <t>355098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403647</t>
+          <t>401736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>495538</t>
+          <t>493890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>545523</t>
+          <t>543682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866530</t>
+          <t>866430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>934244</t>
+          <t>935870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57717</t>
+          <t>56681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87936</t>
+          <t>86942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>146775</t>
+          <t>149532</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200319</t>
+          <t>195683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>215497</t>
+          <t>216369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>274893</t>
+          <t>273059</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199209</t>
+          <t>200203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229428</t>
+          <t>230464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>879311</t>
+          <t>883947</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>932855</t>
+          <t>930098</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1091882</t>
+          <t>1093716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1151278</t>
+          <t>1150406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1114959</t>
+          <t>1113595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1232237</t>
+          <t>1222223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>863563</t>
+          <t>870872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>972091</t>
+          <t>975934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2016271</t>
+          <t>2022076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2170113</t>
+          <t>2177737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2151548</t>
+          <t>2161562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2268826</t>
+          <t>2270190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2554066</t>
+          <t>2550223</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2662594</t>
+          <t>2655285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4739830</t>
+          <t>4732206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4893672</t>
+          <t>4887867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84892</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67970</t>
+          <t>77077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>114103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69178</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57619</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>154070</t>
+          <t>167445</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135218</t>
+          <t>145718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180077</t>
+          <t>188805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>420320</t>
+          <t>456337</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401126</t>
+          <t>436515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437242</t>
+          <t>473541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>378289</t>
+          <t>415247</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>364625</t>
+          <t>400547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389848</t>
+          <t>427421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>798609</t>
+          <t>871584</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772602</t>
+          <t>850224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>817461</t>
+          <t>893311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76825</t>
+          <t>78621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114899</t>
+          <t>117053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83405</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>78342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98977</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>176122</t>
+          <t>187309</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152685</t>
+          <t>162799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198784</t>
+          <t>212462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>359496</t>
+          <t>388412</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337314</t>
+          <t>366159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375388</t>
+          <t>404591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299175</t>
+          <t>330634</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283603</t>
+          <t>315762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312479</t>
+          <t>344801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>658671</t>
+          <t>719046</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>636009</t>
+          <t>693893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>682108</t>
+          <t>743556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>120061</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50170</t>
+          <t>107448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203009</t>
+          <t>147130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33531</t>
+          <t>36601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>154948</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>132833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214137</t>
+          <t>176301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>548203</t>
+          <t>343998</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465255</t>
+          <t>324482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618094</t>
+          <t>364164</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>141419</t>
+          <t>160163</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133380</t>
+          <t>150896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148184</t>
+          <t>167431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>689622</t>
+          <t>504161</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621038</t>
+          <t>482808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>759079</t>
+          <t>526276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>338478</t>
+          <t>363291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>302702</t>
+          <t>329077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>374876</t>
+          <t>400874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>214255</t>
+          <t>231688</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106548</t>
+          <t>207828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278875</t>
+          <t>256293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>552733</t>
+          <t>594979</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348963</t>
+          <t>551603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>630951</t>
+          <t>634569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>696341</t>
+          <t>768552</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>659943</t>
+          <t>730969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>732117</t>
+          <t>802766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>763176</t>
+          <t>628821</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698556</t>
+          <t>604216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>870883</t>
+          <t>652681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1459517</t>
+          <t>1397373</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1381299</t>
+          <t>1357783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1663287</t>
+          <t>1440749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>72,31%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>158697</t>
+          <t>183585</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>158600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181140</t>
+          <t>210013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>158679</t>
+          <t>174095</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120705</t>
+          <t>154471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187122</t>
+          <t>195285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>317376</t>
+          <t>357680</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263009</t>
+          <t>324688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>357680</t>
+          <t>390681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>315319</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>292876</t>
+          <t>356869</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336649</t>
+          <t>408282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>681975</t>
+          <t>656050</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>653532</t>
+          <t>634860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719949</t>
+          <t>675674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>997294</t>
+          <t>1039346</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>956990</t>
+          <t>1006345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1051661</t>
+          <t>1072338</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>26975</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48860</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70758</t>
+          <t>76411</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106932</t>
+          <t>114552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>115131</t>
+          <t>118546</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>97785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142299</t>
+          <t>147022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>210425</t>
+          <t>209111</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190644</t>
+          <t>192192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225652</t>
+          <t>221284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>675319</t>
+          <t>752710</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654439</t>
+          <t>729729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>690613</t>
+          <t>767870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>885744</t>
+          <t>961821</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>858576</t>
+          <t>933345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>908002</t>
+          <t>982582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>823924</t>
+          <t>890545</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>592456</t>
+          <t>830345</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>910701</t>
+          <t>953171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>637061</t>
+          <t>690361</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>526310</t>
+          <t>648871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698694</t>
+          <t>736605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1460985</t>
+          <t>1580906</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1253799</t>
+          <t>1503780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1576625</t>
+          <t>1648576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2550104</t>
+          <t>2549707</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2463327</t>
+          <t>2487081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2781572</t>
+          <t>2609907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2939353</t>
+          <t>2943624</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2877720</t>
+          <t>2897380</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3050104</t>
+          <t>2985114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5489456</t>
+          <t>5493331</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5373816</t>
+          <t>5425661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5696642</t>
+          <t>5570457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
